--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,73 +991,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Directory Audit Ticketing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+          <t>h_01M3NZ460G1TDWM8ZDSMKXC53X</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M3NZ460G1TDWM8ZDSMKXC53X</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>Directory Audit Ticketing Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KWEQA30HHS3MAR554WF8EPGY</t>
+          <t>h_01M3NZ61MF7AS5PKK6FEKFK5ZK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQA30HHS3MAR554WF8EPGY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M3NZ61MF7AS5PKK6FEKFK5ZK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Configure Username Format</t>
+          <t>Rules</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+          <t>h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQ9V50JBM9GDK3DVNXFHVC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Naming</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+          <t>h_01KWEQA30HHS3MAR554WF8EPGY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQA30HHS3MAR554WF8EPGY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Organizational Unit (OU) Assignment Rules</t>
+          <t>Configure Username Format</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+          <t>h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQAKSVX3JJHQ7TZDK0ZFE9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Assignment Rules</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+          <t>h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQFPS1GP3PP20VJSXD1WTW</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Groups Active Directory (Group Rules)</t>
+          <t>Organizational Unit (OU) Assignment Rules</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,41 +1133,41 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KWEQM679F8TVM219RF6MQ3VT</t>
+          <t>h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQM679F8TVM219RF6MQ3VT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQG3BCN8RKBYXC49PQPE5Y</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Assignment Rules</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+          <t>h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQNJ20MXRPW1NF539BGKFC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQJYDV5YBVKJH6DY81SX8Z</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Password Policy Configuration</t>
+          <t>Groups Active Directory (Group Rules)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+          <t>h_01KWEQM679F8TVM219RF6MQ3VT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQM679F8TVM219RF6MQ3VT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Modifying Assignment Rules</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KWER6VNN0BAFH9WG64J126QX</t>
+          <t>h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER6VNN0BAFH9WG64J126QX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KS2314NK832RV0ARBZB3WSEX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KWER73FFYP2KY20YANJSH6M5</t>
+          <t>h_01KWEQNJ20MXRPW1NF539BGKFC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER73FFYP2KY20YANJSH6M5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQNJ20MXRPW1NF539BGKFC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Password Policy Configuration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,63 +1243,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KWER7NV99NHTZXVZTWAA35DR</t>
+          <t>h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER7NV99NHTZXVZTWAA35DR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEQP2GMXEQT9XC3YG8A0SPA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Individual Notifications (Per Record)</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KWERA0YBZKXJH6C73XBM54BK</t>
+          <t>h_01KWER6VNN0BAFH9WG64J126QX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERA0YBZKXJH6C73XBM54BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER6VNN0BAFH9WG64J126QX</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Run Summary Notifications</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
+          <t>h_01KWER73FFYP2KY20YANJSH6M5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER73FFYP2KY20YANJSH6M5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,63 +1309,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KWEREYS2MA70BX7DDADJYF6T</t>
+          <t>h_01KWER7NV99NHTZXVZTWAA35DR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEREYS2MA70BX7DDADJYF6T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWER7NV99NHTZXVZTWAA35DR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Individual Notifications (Per Record)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01M13VMATGG9BVY65KZH6PNP0R</t>
+          <t>h_01KWERA0YBZKXJH6C73XBM54BK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M13VMATGG9BVY65KZH6PNP0R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERA0YBZKXJH6C73XBM54BK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Run Summary Notifications</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M1BHSF1Q3TR6WSXNE8GV60WG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,63 +1375,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>h_01KWEREYS2MA70BX7DDADJYF6T</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEREYS2MA70BX7DDADJYF6T</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>h_01M13VMATGG9BVY65KZH6PNP0R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M13VMATGG9BVY65KZH6PNP0R</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Source Filter Rules</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6CJQCS03KJD036GY6YNQJ7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,120 +1441,252 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KT6C3M0H03QNNJZ9QAA3CHWC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWEE98ZWSRZGSCZ44WB68AE5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Source Filter Rules</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERHBRWQFKB7E87HNF5WT3V</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERMQMEQNYXEHCGTMBYGSWJ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KWERQVHZCVABM2GYKRZ7Q0VT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01M3RYAHF7Z5DSTS1MFHFZ834F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01M3RYAHF7Z5DSTS1MFHFZ834F</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Service Desk Bridge</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Directory-ITSM-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Directory-ITSM-Integration-Guide/headings.xlsx
+++ b/site/Directory-ITSM-Integration-Guide/headings.xlsx
@@ -991,7 +991,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Directory Audit Ticketing</t>
+          <t>JML Ticketing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Directory Audit Ticketing Settings</t>
+          <t>JML Ticketing</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
